--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 4,52</t>
+          <t>-11,89; 4,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,23</t>
+          <t>-4,49; 9,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 13,28</t>
+          <t>-4,35; 12,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,43; 184,07</t>
+          <t>-88,21; 200,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 698,88</t>
+          <t>-58,32; 645,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,55</t>
+          <t>-4,06; 3,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,48</t>
+          <t>1,12; 9,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 5,76</t>
+          <t>-5,29; 6,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 4,56</t>
+          <t>-4,02; 4,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,19 +790,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,02; 305,54</t>
+          <t>-72,3; 299,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 197,5</t>
+          <t>-70,16; 204,38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,16</t>
+          <t>-1,88; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,65</t>
+          <t>-10,19; 0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 0,95</t>
+          <t>-8,88; 1,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,24</t>
+          <t>-100,0; 268,57</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,74</t>
+          <t>-4,55; 3,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 9,24</t>
+          <t>-5,21; 8,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 5,52</t>
+          <t>-15,18; 5,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,69</t>
+          <t>0,25; 6,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 493,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 104,4</t>
+          <t>-85,11; 107,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,18</t>
+          <t>0,0; 30,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 28,06</t>
+          <t>-0,4; 29,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 14,16</t>
+          <t>-6,83; 13,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,26</t>
+          <t>-3,06; 5,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,53; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 0,0</t>
+          <t>-8,23; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 10,78</t>
+          <t>-6,99; 11,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 7,22</t>
+          <t>-3,77; 7,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,93</t>
+          <t>-4,25; 1,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,79</t>
+          <t>-3,29; 1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,34</t>
+          <t>-1,29; 5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,65</t>
+          <t>-8,15; 2,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,42; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-72,43; 57,24</t>
+          <t>-70,58; 57,01</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,04</t>
+          <t>-2,67; 5,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,78</t>
+          <t>-0,39; 5,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,21</t>
+          <t>-3,16; 4,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 7,87</t>
+          <t>-7,03; 7,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 431,4</t>
+          <t>-64,75; 457,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,73; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 216,31</t>
+          <t>-65,23; 221,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 81,86</t>
+          <t>-43,0; 79,14</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,87</t>
+          <t>-2,13; 0,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,37</t>
+          <t>0,07; 3,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,26</t>
+          <t>-1,83; 2,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,79</t>
+          <t>-2,48; 1,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 50,99</t>
+          <t>-60,02; 51,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 423,77</t>
+          <t>-5,64; 386,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 59,16</t>
+          <t>-31,89; 69,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 38,48</t>
+          <t>-36,51; 33,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 4,3</t>
+          <t>-11,35; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 9,41</t>
+          <t>-4,48; 11,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 12,95</t>
+          <t>-4,34; 13,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,21; 200,16</t>
+          <t>-87,13; 160,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,32; 645,43</t>
+          <t>-55,02; 672,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 3,56</t>
+          <t>-4,95; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,06</t>
+          <t>1,14; 9,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,74</t>
+          <t>-6,3; 5,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 4,42</t>
+          <t>-4,21; 4,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 299,48</t>
+          <t>-76,88; 231,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 204,38</t>
+          <t>-71,63; 193,34</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,42</t>
+          <t>-1,87; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 0,8</t>
+          <t>-9,85; 1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 1,92</t>
+          <t>-9,08; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,57</t>
+          <t>-100,0; 86,58</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,0</t>
+          <t>-3,93; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,74</t>
+          <t>-5,34; 9,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 5,28</t>
+          <t>-14,98; 5,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,99</t>
+          <t>0,24; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 493,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 107,87</t>
+          <t>-83,31; 102,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,34</t>
+          <t>0,0; 34,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 29,49</t>
+          <t>-1,35; 31,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 13,28</t>
+          <t>-6,95; 13,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,17</t>
+          <t>-3,11; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 902,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 0,0</t>
+          <t>-8,16; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 11,17</t>
+          <t>-6,9; 10,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 7,47</t>
+          <t>-3,91; 7,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,39</t>
+          <t>-4,2; 1,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,8</t>
+          <t>-3,3; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,65</t>
+          <t>-1,5; 5,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,56</t>
+          <t>-8,23; 2,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 330,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,42; —</t>
+          <t>-70,86; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 57,01</t>
+          <t>-71,47; 63,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 5,71</t>
+          <t>-2,78; 5,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,69</t>
+          <t>-0,39; 5,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,49</t>
+          <t>-2,91; 4,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 7,9</t>
+          <t>-6,53; 7,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 457,43</t>
+          <t>-71,64; 418,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,73; —</t>
+          <t>-73,0; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 221,15</t>
+          <t>-60,57; 224,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 79,14</t>
+          <t>-41,36; 74,63</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,93</t>
+          <t>-2,07; 1,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,22</t>
+          <t>0,19; 3,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,56</t>
+          <t>-1,99; 2,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,6</t>
+          <t>-2,28; 1,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 51,67</t>
+          <t>-60,37; 56,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 386,7</t>
+          <t>2,47; 391,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 69,55</t>
+          <t>-34,43; 66,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 33,81</t>
+          <t>-33,39; 41,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 4,13</t>
+          <t>-11,74; 4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 11,08</t>
+          <t>-4,41; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 13,55</t>
+          <t>-3,26; 13,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-87,13; 160,4</t>
+          <t>-86,43; 184,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 672,37</t>
+          <t>-48,64; 698,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,81</t>
+          <t>-4,11; 3,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,59</t>
+          <t>1,14; 10,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 5,65</t>
+          <t>-6,41; 5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,55</t>
+          <t>-2,9; 6,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 231,45</t>
+          <t>-79,02; 305,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,63; 193,34</t>
+          <t>-60,16; 287,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-3,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-61,69%</t>
+          <t>-63,71%</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,99</t>
+          <t>-1,87; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 1,39</t>
+          <t>-10,05; 0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,04</t>
+          <t>-10,01; 0,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,58</t>
+          <t>-100,0; 145,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,85</t>
+          <t>-4,27; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 9,58</t>
+          <t>-4,86; 9,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 5,32</t>
+          <t>-15,43; 5,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,03</t>
+          <t>0,51; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,31; 102,12</t>
+          <t>-85,47; 104,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,1</t>
+          <t>0,0; 29,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 31,38</t>
+          <t>-0,24; 28,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 13,4</t>
+          <t>-5,72; 14,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,12</t>
+          <t>-2,97; 5,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 902,86</t>
+          <t>-80,53; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 0,0</t>
+          <t>-7,39; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 10,61</t>
+          <t>-7,22; 10,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 7,43</t>
+          <t>-4,96; 6,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-28,41%</t>
+          <t>-25,08%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,42</t>
+          <t>-4,26; 1,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,77</t>
+          <t>-2,93; 1,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,48</t>
+          <t>-1,75; 5,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 2,98</t>
+          <t>-8,19; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-70,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 63,17</t>
+          <t>-71,29; 58,99</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,25</t>
+          <t>-2,91; 5,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,71</t>
+          <t>-0,5; 5,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,56</t>
+          <t>-3,3; 4,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 7,54</t>
+          <t>-6,76; 7,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,64; 418,65</t>
+          <t>-68,66; 431,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 224,12</t>
+          <t>-66,41; 216,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 74,63</t>
+          <t>-41,01; 83,75</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,94%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,03</t>
+          <t>-2,11; 0,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,32</t>
+          <t>0,19; 3,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,5</t>
+          <t>-1,92; 2,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,9</t>
+          <t>-2,39; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 56,46</t>
+          <t>-59,06; 50,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 391,45</t>
+          <t>3,81; 423,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 66,33</t>
+          <t>-32,91; 59,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 41,64</t>
+          <t>-33,13; 43,22</t>
         </is>
       </c>
     </row>
